--- a/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="La-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ge-Ge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Rh-Ge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="U-In" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="U-Rh" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Rh-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="In-In" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Pr-Ge" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Pt-Pt" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Sm-Ge" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Nd-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Ru-Ge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Tb-Ge" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Eu-Ge" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,13 +467,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>554038.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>2.401</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>560709 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -674,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,15 +802,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1923821.cif</t>
+          <t>300162 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.819</v>
+        <v>3.161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -743,15 +863,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>1923821.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.141</v>
+        <v>2.819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -789,11 +909,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.157</v>
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -812,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,13 +955,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300163.cif</t>
+          <t>300161 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.507</v>
+        <v>3.157</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.157</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -881,11 +1016,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>300163.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.135</v>
+        <v>2.507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -896,11 +1031,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300163.cif</t>
+          <t>300163 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.187</v>
+        <v>2.507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,13 +1077,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.161</v>
+        <v>3.135</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.187</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300163 2.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.187</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -965,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,9 +1157,99 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2.482</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>560709 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -1057,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,13 +1335,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>560709 2.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>554038.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B5" t="n">
         <v>3.332</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -1098,249 +1413,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.482</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1369,6 +1441,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>560709 2.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709 2.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>554038 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300163 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300161 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300162 2.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>300156.cif</t>
         </is>
       </c>
@@ -1414,7 +1879,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300161 2.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1429,11 +1894,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.519</v>
+        <v>2.515</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1444,13 +1909,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>300162 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>300159.cif</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B9" t="n">
         <v>2.538</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>

--- a/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
@@ -7,19 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="La-Ga" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="La-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ge-Ge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Rh-Ge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="U-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="U-Rh" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Rh-Rh" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="In-In" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Rh-In" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="In-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="U-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Pr-Ge" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Pt-Pt" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Sm-Ge" sheetId="16" state="visible" r:id="rId16"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,26 +467,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>560709 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.358</v>
+        <v>2.979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.401</v>
+        <v>2.979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -497,15 +497,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554038 2.cif</t>
+          <t>539016.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.401</v>
+        <v>3.291</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.482</v>
+        <v>3.332</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -531,54 +531,9 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.482</v>
+        <v>3.332</v>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>560709 2.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -1312,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1335,26 +1290,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709 2.cif</t>
+          <t>539016.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.979</v>
+        <v>2.358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.979</v>
+        <v>2.401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1365,15 +1320,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>554038 2.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.291</v>
+        <v>2.401</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1339,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.332</v>
+        <v>2.482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1399,9 +1354,54 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.332</v>
+        <v>2.482</v>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>560709 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -1630,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,11 +1653,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300163.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.233</v>
+        <v>2.481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300163 2.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.233</v>
+        <v>2.495</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300156.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.304</v>
+        <v>2.499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1698,11 +1698,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>300161 2.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.323</v>
+        <v>2.515</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1713,11 +1713,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.329</v>
+        <v>2.515</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1728,11 +1728,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300161 2.cif</t>
+          <t>300162 2.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.352</v>
+        <v>2.519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1743,11 +1743,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300162.cif</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.352</v>
+        <v>2.519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1758,43 +1758,13 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300162 2.cif</t>
+          <t>300159.cif</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.359</v>
+        <v>2.538</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -1811,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1834,11 +1804,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300156.cif</t>
+          <t>300163.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.481</v>
+        <v>2.233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1849,11 +1819,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>300163 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.495</v>
+        <v>2.233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1864,11 +1834,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.499</v>
+        <v>2.304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1879,11 +1849,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300161 2.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.515</v>
+        <v>2.323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1894,11 +1864,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.515</v>
+        <v>2.329</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1909,11 +1879,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300162 2.cif</t>
+          <t>300161 2.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.519</v>
+        <v>2.352</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1924,11 +1894,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.519</v>
+        <v>2.352</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1939,13 +1909,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>300162 2.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>300159.cif</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.538</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B11" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>

--- a/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
@@ -7,19 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="16" state="visible" r:id="rId16"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,21 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -980,44 +995,257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>560709.cif</t>
         </is>
       </c>
@@ -1030,27 +1258,194 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.601</v>
+        <v>2.499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1079,72 +1474,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.179</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.291</v>
+        <v>2.304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1155,254 +1550,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.332</v>
+        <v>2.323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.358</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.499</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.515</v>
+        <v>2.329</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1413,11 +1580,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.519</v>
+        <v>2.352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1428,173 +1595,6 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.538</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>300162.cif</t>
         </is>
       </c>

--- a/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
@@ -10,23 +10,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,6 +775,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1923821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1923821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>300160.cif</t>
         </is>
       </c>
@@ -790,7 +884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -836,7 +930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -882,7 +976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -911,21 +1005,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>300163.cif</t>
         </is>
       </c>
@@ -943,7 +1098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -989,40 +1144,86 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1033,11 +1234,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.332</v>
+        <v>2.501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1045,58 +1246,27 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.179</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1125,21 +1295,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>560709.cif</t>
         </is>
       </c>
@@ -1152,227 +1398,196 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300156.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.601</v>
+        <v>2.499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.501</v>
+        <v>2.304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.358</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.499</v>
+        <v>2.323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1383,11 +1598,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.515</v>
+        <v>2.329</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1398,11 +1613,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.519</v>
+        <v>2.352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1413,127 +1628,6 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.539</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>300162.cif</t>
         </is>
       </c>

--- a/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
@@ -7,21 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,26 +469,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.358</v>
+        <v>2.401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.401</v>
+        <v>2.501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -497,46 +497,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.451</v>
+      </c>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.42</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1592,7 +1577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1615,59 +1600,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>539016.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.401</v>
+        <v>2.358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>560709.cif</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>2.501</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.451</v>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1675,6 +1675,109 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>560709.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554038.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.201</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1756,109 +1859,6 @@
         <v>0.25</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>539016.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.291</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>554038.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.201</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="In-In" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="U-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
+++ b/20240308_output_test/output/20240308_output_test_element_pairs.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ge-Ge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Ho-Ge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="In-In" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="U-In" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Rh-In" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="U-Rh" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Rh-Rh" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-In" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-Rh" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U-In" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sn" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sn-Sn" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,31 +497,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>539016.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.451</v>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1267,26 +1282,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>539016.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.401</v>
+        <v>2.358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.501</v>
+        <v>2.401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1297,11 +1312,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.601</v>
+        <v>2.501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1321,7 +1336,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.501</v>
+        <v>2.42</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -1332,7 +1347,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.073</v>
       </c>
       <c r="C7" t="inlineStr"/>
     </row>
@@ -1577,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1600,15 +1615,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>539016.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.358</v>
+        <v>2.979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1634,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.401</v>
+        <v>3.332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1628,46 +1643,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>560709.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.156</v>
+      </c>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1806,11 +1806,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>560709.cif</t>
+          <t>554038.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.979</v>
+        <v>2.401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1821,11 +1821,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>554038.cif</t>
+          <t>560709.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.332</v>
+        <v>2.501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.156</v>
+        <v>2.451</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -2019,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2042,11 +2042,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300163.cif</t>
+          <t>300156.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.233</v>
+        <v>3.12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2055,121 +2055,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300156.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.304</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+        <v>3.12</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2182,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2205,42 +2113,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>300156.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Full occupancy</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>300158.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2.323</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
